--- a/travellens/reports/LABEL_THESE_annotator1.xlsx
+++ b/travellens/reports/LABEL_THESE_annotator1.xlsx
@@ -519,7 +519,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>You are reading one PIECE of a review and saying whether the visitor is complaining about any of four things.</t>
+          <t>You are reading one PIECE of a review and saying whether the visitor is complaining about any of 4 things.</t>
         </is>
       </c>
     </row>
@@ -529,35 +529,35 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>The four columns</t>
+          <t>The 4 columns</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Roads &amp; access   roads, parking, buses, the walk, signage, finding it</t>
+          <t>Roads &amp; access     roads, parking, buses, the walk, signage, finding it</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Cleanliness      litter, plastic, smells, upkeep</t>
+          <t>Cleanliness        litter, plastic, smells, upkeep</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Facilities       toilets, food, seating, shelter, bins, guides</t>
+          <t>Facilities         toilets, food, seating, shelter, bins, guides</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Safety           slippery ground, deep water, wildlife, warnings</t>
+          <t>Safety             slippery ground, deep water, wildlife, warnings</t>
         </is>
       </c>
     </row>
